--- a/data/seed/portfolio/L-2024-6651/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6651/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>31207000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>15654000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Jizzax Non MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>316537565</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000459635185001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №299/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №204/26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>2716000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>17587000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>250498122</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000111595253001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №127/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №4776</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,33 +640,33 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>26591000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>28024000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №258/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №84/26</t>
         </is>
       </c>
     </row>
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>6486000</v>
+        <v>7863000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>225983768</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000398416255001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №25/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №33/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,33 +722,33 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>41076000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>235488000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №88/26</t>
+          <t>Оплата за продукцию по договору №294/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -763,23 +763,23 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>24896000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>17006000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №137/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №6919</t>
         </is>
       </c>
     </row>
@@ -804,23 +804,18 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>17210000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>61957000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>336381017</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -830,14 +825,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №456</t>
+          <t>Iyun oyi uchun ish haqi, reestr №9481</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -845,23 +840,23 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>15152000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>57877000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -871,14 +866,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №5364</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -888,38 +883,38 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>2721000</v>
+        <v>58356000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shartnoma №224/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №184/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -928,22 +923,22 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>25877000</v>
+        <v>10463000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Ishonch Polimer MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>338545479</t>
+          <t>354547961</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>20208000492785349001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -953,14 +948,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2462</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №171/26, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,35 +963,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>61957000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>32828000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Предоплата за товар по дог. №13/26 от 09.07.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,23 +1004,23 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>10841000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>5571000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Jizzax Qurilish AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>372680968</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000626285591001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,14 +1030,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6574</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №56/24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,40 +1045,40 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>5571000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>12294000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shodlik Qurilish Materiallari MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>334816537</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000654459635001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Предоплата за товар по дог. №259/26 от 10.07.2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,38 +1088,38 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>7720000</v>
+        <v>15643000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7772 08.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7814</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,23 +1127,23 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>5728000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>9444000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1153,14 +1153,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №82/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №9824</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1169,22 +1169,22 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>26978000</v>
+        <v>14622000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shahrisabz Moy MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>389960988</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000092788144001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7083</t>
+          <t>Оплата за товары согласно счет-фактуре №3815</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1210,22 +1210,22 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>88308000</v>
+        <v>174926000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1235,14 +1235,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9856</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №243/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1252,21 +1252,21 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>9371000</v>
+        <v>75895000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №3328 ОТ 09.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №1239 15.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,38 +1293,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>3825000</v>
+        <v>23671000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5895</t>
+          <t>Shartnoma №278/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1333,39 +1333,39 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>42291000</v>
+        <v>8449000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samarqand Polimer XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>297451020</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000539670060001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №181/26</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>52651000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>8449000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1484</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1416,38 +1416,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>19141000</v>
+        <v>7673000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3155 13.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №64/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,23 +1455,23 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>4214000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>10535000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1481,14 +1481,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4368 13.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №120/26 от 17.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>5034000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>11404000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №253/26, QS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №21/26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,40 +1537,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>8449000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>94011000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Shartnoma №216/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,40 +1578,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>8449000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>19002000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1619,40 +1619,40 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>200071000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>15760000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Olmaliq Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>345102085</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000967006073001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №134/26</t>
+          <t>Shartnoma №95/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1662,21 +1662,21 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>44754000</v>
+        <v>9109000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>228856334</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000040162863001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7483</t>
+          <t>Mahsulot uchun to'lov, shartnoma №222/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1703,38 +1703,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>6037000</v>
+        <v>13519000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Urganch Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>379533287</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000374727388001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4014 17.07.2026, QQS bilan</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №221/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,40 +1742,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>29967000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>34636000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Ishonch Polimer MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>354547961</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000492785349001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №102/26, QQS 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №143/26, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1783,40 +1783,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>20251000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>56773000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>250498122</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000111595253001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8547 20.07.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №92/26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1824,40 +1824,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>12507000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>3482000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000311286575001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №65/26, QQS 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1865,40 +1865,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>10216000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>8733000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1906,23 +1906,23 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>5627000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>12402000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №114/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №112/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1949,38 +1949,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>5266000</v>
+        <v>21478000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Navro'z Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>364288563</t>
+          <t>222688499</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000450401628001</t>
+          <t>20208000278298633001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №70/26, QQS 12%</t>
+          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1988,40 +1988,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>2634000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №16/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5828</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>25.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2029,23 +2029,18 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>2545000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>336381017</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6651)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>16307000318003298417</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2055,14 +2050,14 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №230/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-6651 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2070,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>35792000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>16042000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Urganch Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>379533287</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000374727388001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №130/26</t>
+          <t>Shartnoma №1/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2113,38 +2108,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>15862000</v>
+        <v>14015000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SHARTNOMA №134/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Shartnoma №111/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2152,23 +2147,23 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>25488000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>103929000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2178,14 +2173,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6610</t>
+          <t>Tovarlar uchun to'lov h/f №580</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2195,38 +2190,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>5053000</v>
+        <v>10689000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Shartnoma №201/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №4165 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2234,40 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>63978000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>14934000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Shartnoma №225/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №154/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2275,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>3482000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>26873000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000856513435001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uhun to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4115 30.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2316,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>9126000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>17510000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №937</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2358,39 +2353,34 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>22341000</v>
+        <v>300000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>338545479</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №32/26</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2398,35 +2388,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>47300000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>64883000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6651)</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>16307000318003298417</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6651 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Предоплата за товар по договору №164/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,21 +2431,21 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>2683000</v>
+        <v>28528000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2455,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №275/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9066</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2477,38 +2472,38 @@
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>3938000</v>
+        <v>5825000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1333 28.07.2026, QQS bilan</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №238/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,38 +2513,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>2635000</v>
+        <v>4907000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>364288563</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000450401628001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №597 28.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №102/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2558,39 +2553,39 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>136109000</v>
+        <v>8586000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №250/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №10/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2593,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>2819000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>81056000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>250498122</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000111595253001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №272/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №35/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2641,38 +2636,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>207009000</v>
+        <v>4883000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7271</t>
+          <t>Оплата по счет-фактуре №2857 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,40 +2675,35 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>29747000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>58271000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>350066388</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Shartnoma №235/26 bo'yicha oldindan to'lov</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2721,40 +2711,40 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>11627000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>62426000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Angren Yog'och MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>301873517</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000389109902001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №264/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №44/26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2762,40 +2752,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>4366000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>12117000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Nihol Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>235577319</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000192939347001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6336 31.07.2026, QQS bilan</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №9415</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2804,17 +2794,22 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>300000</v>
+        <v>97539000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2824,14 +2819,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Плата за SMS-иформирование</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №53/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2841,38 +2836,38 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>40527000</v>
+        <v>4637000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guliston Polimer MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>291995065</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000549923268001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3839</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2880,23 +2875,23 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>18787000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>6003000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2906,14 +2901,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №286/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №68/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2921,40 +2916,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>9621000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>8008000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Ehtiyot MChJ</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>212226884</t>
+          <t>250498122</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000982782986001</t>
+          <t>20208000111595253001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Shartnoma №268/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №6961</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2963,39 +2958,39 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>13761000</v>
+        <v>10517000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>338545479</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1213</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №53/26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3003,40 +2998,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>15468000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>7597000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>338545479</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №253/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3508 07.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3045,39 +3040,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>15485000</v>
+        <v>10956000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Jizzax Non MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>338545479</t>
+          <t>316537565</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>20208000459635185001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №275/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №269/26</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3086,39 +3081,39 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>35822000</v>
+        <v>15054000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №194/26, QQS bilan</t>
+          <t>Оплата за сырье по дог. №181/26 от 07.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3126,40 +3121,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>25052000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>72543000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №200/26, QQS 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №109/26, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3169,38 +3164,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>9424000</v>
+        <v>48880000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №245/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №102/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3208,40 +3203,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>8983000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>12046000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shahrisabz Moy MChJ</t>
+          <t>Navro'z Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>389960988</t>
+          <t>222688499</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000092788144001</t>
+          <t>20208000278298633001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №56/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №167/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3249,18 +3244,23 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>58271000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>6599000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Olmaliq Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>345102085</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000967006073001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3270,14 +3270,14 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №6851</t>
+          <t>Shartnoma №182/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3287,21 +3287,21 @@
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>55931000</v>
+        <v>4806000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>307997219</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000833833599001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,14 +3311,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №248/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5377 10.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3326,33 +3326,33 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>5240000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>4305000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shodlik Qurilish Materiallari MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>334816537</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000654459635001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №44/21</t>
+          <t>Mahsulot uchun to'lov, shartnoma №204/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -3367,33 +3367,33 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>32912000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>5240000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Jizzax Qurilish AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>372680968</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000626285591001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Shartnoma №158/26 bo'yicha oldindan to'lov</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
@@ -3408,33 +3408,33 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>14894000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>25774000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shartnoma №23/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №916</t>
         </is>
       </c>
     </row>
@@ -3449,23 +3449,23 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>8440000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>52263000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Jizzax Non MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>316537565</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000459635185001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3475,14 +3475,14 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Shartnoma №154/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №7188</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3490,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>8999000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>27648000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Olmaliq Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>345102085</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000967006073001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №269/26</t>
+          <t>Tovar uchun to'lov, h/f №5638 11.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3532,39 +3532,39 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>20079000</v>
+        <v>13483000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №39/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №138/26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3573,39 +3573,39 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>24512000</v>
+        <v>32691000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6819</t>
+          <t>Оплата за упаковочные материалы, с/ф №3242</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3613,40 +3613,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>31160000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>7042000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Lazzat Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>299506565</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000992326804001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №382 12.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3654,23 +3654,23 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>16066000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>6531000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shahrisabz Moy MChJ</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>389960988</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000092788144001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №23/26</t>
+          <t>Tovar uchun to'lov, h/f №5161 12.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,23 +3695,23 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>28094000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>65944000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №233/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2326</t>
         </is>
       </c>
     </row>
@@ -3736,33 +3736,33 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>13806000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>17957000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>364288563</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000450401628001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №7/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №37/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -3779,31 +3779,31 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>14104000</v>
+        <v>16707000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2060 14.08.2026, QQS bilan</t>
+          <t>Shartnoma №224/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -3818,33 +3818,33 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>7946000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>12708000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Shartnoma №141/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -3885,14 +3885,14 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3900,40 +3900,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>129298000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>7946000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zafar Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>235079972</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000958338335001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №13/26, QQS 12%</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3941,33 +3941,33 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>73380000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>12967000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №198/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №281/26</t>
         </is>
       </c>
     </row>
@@ -3984,21 +3984,21 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>24916000</v>
+        <v>12465000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1667</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8584</t>
         </is>
       </c>
     </row>
@@ -4023,33 +4023,33 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>36021000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>9582000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Farovon Un Mahsulotlari AJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>210601961</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000502150158001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №249/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2910</t>
         </is>
       </c>
     </row>
@@ -4064,33 +4064,33 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>37523000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>8196000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №78/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2621</t>
         </is>
       </c>
     </row>
@@ -4105,40 +4105,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>111608000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>3976000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5755</t>
+          <t>Mahsulot uchun to'lov, shartnoma №119/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4146,23 +4146,23 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>12806000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>16349000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>364288563</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000450401628001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4172,14 +4172,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shartnoma №275/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №238/26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4188,32 +4188,32 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>16046000</v>
+        <v>32310000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №121</t>
+          <t>Оплата за транспортные услуги по договору №151/26</t>
         </is>
       </c>
     </row>
@@ -4228,23 +4228,23 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>76107000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>4113000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4254,14 +4254,14 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №32/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7989</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4271,38 +4271,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>68785000</v>
+        <v>16717000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Navro'z Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>222688499</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000278298633001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8146 24.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №423</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4312,21 +4312,21 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>9573000</v>
+        <v>69960000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Lazzat Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>299506565</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000992326804001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4336,14 +4336,14 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №135/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №9037 20.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4351,40 +4351,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>8323000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>7788000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7398</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4394,38 +4394,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>15007000</v>
+        <v>7655000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №122/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №4/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4433,40 +4433,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>3275000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>35085000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000856513435001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №43/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4474,40 +4474,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>14339000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>24466000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>393808423</t>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000410475433001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №18/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4515,35 +4515,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>47300000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>18508000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6651)</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>16307000318003298417</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6651 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1936</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4553,38 +4558,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>95833000</v>
+        <v>12778000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №181/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8713 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4599,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>9092000</v>
+        <v>3965000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Urganch Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>379533287</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000374727388001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6165</t>
+          <t>Оплата за товар по с/ф №227 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4633,40 +4638,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>11420000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>3275000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000311286575001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1421</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4675,34 +4680,39 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>300000</v>
+        <v>8490000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,40 +4720,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>12995000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>16787000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>338545479</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4190</t>
+          <t>Shartnoma №48/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4751,40 +4761,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>20112000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>11263000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №209/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2462</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4793,39 +4803,34 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>21274000</v>
+        <v>47300000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>282266318</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6651)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>16307000318003298417</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №7947</t>
+          <t>Kredit shartnomasi L-2024-6651 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4833,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>28503000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>13525000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4704</t>
+          <t>Оплата за товар по с/ф №4340 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4876,38 +4881,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>5201000</v>
+        <v>22990000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Shartnoma №186/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №220/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4915,40 +4920,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>23375000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>20671000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №123/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4603 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4958,21 +4963,21 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>7059000</v>
+        <v>19345000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4982,14 +4987,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №190/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №429</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4999,38 +5004,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4968000</v>
+        <v>7564000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>206638855</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000231675921001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4734 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartn. №185/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5040,38 +5045,38 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>11789000</v>
+        <v>7194000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Ehtiyot MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>212226884</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000982782986001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3931</t>
+          <t>Mahsulot uchun to'lov, shartnoma №172/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5079,40 +5084,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>11703000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>7106000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Farovon Un Mahsulotlari AJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>210601961</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000502150158001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3114</t>
+          <t>Shartnoma №50/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5120,40 +5125,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>37325000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>5948000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>338545479</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000154927853001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №134</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2819</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5163,38 +5168,38 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>17968000</v>
+        <v>5386000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №48/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №244/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5203,7 +5208,7 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>61501000</v>
+        <v>300000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
@@ -5223,14 +5228,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5240,38 +5245,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>35373000</v>
+        <v>13296000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №261/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2259</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5279,40 +5284,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>32478000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>24793000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zafar Polimer MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>235079972</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000958338335001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №5301</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5322,38 +5327,38 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>25124000</v>
+        <v>2742000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6440 07.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №15/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5363,38 +5368,38 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>12658000</v>
+        <v>9723000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Navro'z Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>222688499</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000278298633001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6323</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5754</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5404,31 +5409,31 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>4660000</v>
+        <v>9649000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>364288563</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000450401628001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1570</t>
+          <t>Оплата по счет-фактуре №7841 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -5443,33 +5448,33 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>23096000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>16062000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №121/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9586</t>
         </is>
       </c>
     </row>
@@ -5484,23 +5489,23 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>143629000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>5002000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5510,14 +5515,14 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №172/26</t>
+          <t>Оплата по счет-фактуре №759 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5527,38 +5532,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>4968000</v>
+        <v>3755000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chust Mehmonxona XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>350066388</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000522316759001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9329 08.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3114</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,23 +5571,23 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>23719000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>8435000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5592,14 +5597,14 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1768 09.09.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №9539</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5607,40 +5612,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>9037000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>40571000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Shahrisabz Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338192460</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000812329325001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7576 09.09.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №143/26</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5649,39 +5654,34 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>5530000</v>
+        <v>61501000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shodlik Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>334816537</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000654459635001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №44/21</t>
+          <t>ISH HAQI TO'LOVI AVGUST 2026 (PLASTIK KARTALARGA)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5689,40 +5689,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>9521000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>11005000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis XK</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>393808423</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000410475433001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №47/26 от 09.09.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4489 08.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5731,22 +5731,22 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>16730000</v>
+        <v>5530000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shahrisabz Moy MChJ</t>
+          <t>Jizzax Qurilish AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>389960988</t>
+          <t>372680968</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000092788144001</t>
+          <t>20208000626285591001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №203/26</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5771,40 +5771,40 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>42115000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>211962000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mehnat Sut Mahsulotlari XK</t>
+          <t>Jizzax Non MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>263834900</t>
+          <t>316537565</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000863849520001</t>
+          <t>20208000459635185001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6328 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №2/26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5814,38 +5814,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>6079000</v>
+        <v>20394000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №206/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5331 09.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5855,21 +5855,21 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>69601000</v>
+        <v>12134000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5879,14 +5879,14 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7386</t>
+          <t>Оплата по с/ф №7166 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5896,38 +5896,38 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>14113000</v>
+        <v>3314000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №88/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3762</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>6894000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>3470000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>225983768</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000398416255001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Shartnoma №58/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №62/26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5976,40 +5976,40 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>8387000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>41795000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>307997219</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000833833599001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7194</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6017,40 +6017,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>8387000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>13439000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>JSHDS AVGUST OYI UCHUN</t>
+          <t>Оплата по с/ф №4343 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6060,21 +6060,21 @@
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>108927000</v>
+        <v>6313000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6084,14 +6084,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4410 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №56/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6099,40 +6099,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>4288000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>8387000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №786 21.09.2026, QQS bilan</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>9535000</v>
+        <v>8387000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6183,38 +6183,38 @@
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>18948000</v>
+        <v>47452000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №76/26 от 22.09.2026</t>
+          <t>Предоплата за товар по договору №197/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6224,38 +6224,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>6002000</v>
+        <v>6558000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sharq Qurilish Materiallari MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>345505038</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000701745071001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №226/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9730</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6263,40 +6263,40 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>9590000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>2811000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ziyo Plastik XK</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>389795332</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000753747273001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №160/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3940</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6304,23 +6304,23 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>262107000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>2831000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6330,14 +6330,14 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №106/26</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6345,23 +6345,23 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>23579000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>11604000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6371,14 +6371,14 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №74/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №240/26</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6388,38 +6388,38 @@
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>4797000</v>
+        <v>23390000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Ehtiyot MChJ</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>212226884</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000982782986001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SHARTNOMA №272/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4098 18.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6427,35 +6427,40 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>47300000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>11290000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6651)</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>16307000318003298417</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6651 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Shartnoma №215/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6465,38 +6470,38 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>10438000</v>
+        <v>10786000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №349</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3399</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6506,38 +6511,38 @@
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>7526000</v>
+        <v>3127000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis XK</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>336381017</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000889774572001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7347 28.09.2026, QQS bilan</t>
+          <t>Shartnoma №79/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6545,40 +6550,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>4612000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>253923000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>205860541</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000512608773001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №4794 28.09.2026, QQS BILAN</t>
+          <t>Tovarlar uchun to'lov h/f №7957</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6586,40 +6591,40 @@
           <t>248</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>3456000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>363547000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000856513435001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6776</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6629,21 +6634,21 @@
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>9543000</v>
+        <v>48308000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kamalak Agro MChJ</t>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>371885100</t>
+          <t>338101738</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000432459754001</t>
+          <t>20208000977457251001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6653,14 +6658,14 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №168/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №6130 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6668,18 +6673,23 @@
           <t>250</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>37527000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Yulduz Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>288510074</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000245975499001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6689,14 +6699,14 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>КОМИССИЯ БАНКА ЗА РАСЧЕТНО-КАССОВОЕ ОБСЛУЖИВАНИЕ ЗА СЕНТЯБРЬ</t>
+          <t>Shartnoma №56/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6704,23 +6714,23 @@
           <t>251</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>12559000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>2817000</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>283490098</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000384952031001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6730,14 +6740,14 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8165 21.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6746,58 +6756,868 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>318433000</v>
+        <v>6628000</v>
       </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sarbon Meva Eksport MChJ</t>
+          <t>Ishonch Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>282266318</t>
+          <t>250498122</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000946125478001</t>
+          <t>20208000111595253001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №177/26</t>
+          <t>Оплата за сырье по договору №70/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="n">
-        <v>2245392000</v>
-      </c>
-      <c r="D163" s="4" t="n">
-        <v>2248692000</v>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>2671000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Olmaliq Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>345102085</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000967006073001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5900 ОТ 22.09.2026, В Т.Ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>14490000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8103 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>3390000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №7427 от 23.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>4711000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Shahrisabz Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>338192460</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000812329325001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №7880</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>9599000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>QQS avgust 2026 uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>3669000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Lazzat Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>299506565</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000992326804001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №35/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>3636000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Shartnoma №193/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>3308000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №285/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>9831000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>205860541</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000512608773001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №273/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>47300000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6651)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>16307000318003298417</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2024-6651 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>4886000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Yulduz Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>288510074</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000245975499001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №122/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>4588000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>3073000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №1567 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>3456000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000311286575001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>10455000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>205860541</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000512608773001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №8268</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>12293000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ishonch Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>250498122</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000111595253001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №187/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n">
+        <v>13109000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tovar uchun tolov, h/f №4817 29.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n">
+        <v>4379000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Yangi Hayot Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>350503897</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000174507192001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Shartnoma №211/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>12506000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Chirchiq Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>338101738</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000977457251001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №178/26 от 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Zarafshon Kredit Bank</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Hisob-kassa xizmati uchun haq</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>2231869000</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>2235169000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C164" s="4" t="n">
+      <c r="C184" s="4" t="n">
         <v>225300000</v>
       </c>
-      <c r="D164" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
